--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88654</v>
+        <v>88722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>126986908</v>
       </c>
       <c r="B11" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88722</v>
+        <v>88728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>126986908</v>
       </c>
       <c r="B11" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88728</v>
+        <v>88729</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>126986908</v>
       </c>
       <c r="B11" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1631,60 +1631,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126986901</v>
+        <v>126986908</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>91780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
+          <t>Ottsjö, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402404</v>
+        <v>402449</v>
       </c>
       <c r="R10" t="n">
-        <v>7011782</v>
+        <v>7012086</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1711,27 +1702,18 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1750,51 +1732,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126986908</v>
+        <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>91780</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ottsjö, Jmt</t>
+          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402449</v>
+        <v>402404</v>
       </c>
       <c r="R11" t="n">
-        <v>7012086</v>
+        <v>7011782</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1821,18 +1812,27 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88729</v>
+        <v>88733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126986908</v>
       </c>
       <c r="B10" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1634,7 +1634,7 @@
         <v>126986908</v>
       </c>
       <c r="B10" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Sten Svantesson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Sten Svantesson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Sten Svantesson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1624,7 +1624,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Samuel Persson</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Samuel Persson</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Samuel Persson</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Sten Svantesson, Samuel Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sten Svantesson, Samuel Persson</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1533,7 +1533,7 @@
         <v>126986909</v>
       </c>
       <c r="B9" t="n">
-        <v>88735</v>
+        <v>88722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1631,51 +1631,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126986908</v>
+        <v>126986901</v>
       </c>
       <c r="B10" t="n">
-        <v>91786</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottsjö, Jmt</t>
+          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402449</v>
+        <v>402404</v>
       </c>
       <c r="R10" t="n">
-        <v>7012086</v>
+        <v>7011782</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,18 +1711,27 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1732,60 +1750,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126986901</v>
+        <v>126986908</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>91773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
+          <t>Ottsjö, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402404</v>
+        <v>402449</v>
       </c>
       <c r="R11" t="n">
-        <v>7011782</v>
+        <v>7012086</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1812,27 +1821,18 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -1735,7 +1735,7 @@
         <v>126986901</v>
       </c>
       <c r="B11" t="n">
-        <v>57864</v>
+        <v>57878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73149478</v>
+        <v>126986909</v>
       </c>
       <c r="B2" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103035</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högåsvägen, Ottsjö, Jmt</t>
+          <t>Ottsjö, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>402283.8342165512</v>
+        <v>402449</v>
       </c>
       <c r="R2" t="n">
-        <v>7011509.812200738</v>
+        <v>7012086</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>73149496</v>
+        <v>126986908</v>
       </c>
       <c r="B3" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,49 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högåsvägen, Ottsjö, Jmt</t>
+          <t>Ottsjö, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>402283.8342165512</v>
+        <v>402449</v>
       </c>
       <c r="R3" t="n">
-        <v>7011509.812200738</v>
+        <v>7012086</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,50 +858,46 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>73149508</v>
+        <v>73260110</v>
       </c>
       <c r="B4" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103042</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,14 +907,14 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>132</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>sträckande S</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -975,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>402283.8342165512</v>
+        <v>402284</v>
       </c>
       <c r="R4" t="n">
-        <v>7011509.812200738</v>
+        <v>7011510</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-09-16</t>
+          <t>2018-09-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,65 +996,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>78559940</v>
+        <v>85376911</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högåsvägen, Ottsjö, Jmt</t>
+          <t>Högåsvägen N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>402283.8342165512</v>
+        <v>402278</v>
       </c>
       <c r="R5" t="n">
-        <v>7011509.812200738</v>
+        <v>7011573</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1129,22 +1069,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2019-06-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-05-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringbarkad gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,34 +1088,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Ingela Källén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maud Tyboni</t>
+          <t>Ingela Källén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>85376911</v>
+        <v>126986901</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1205,28 +1134,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högåsvägen N, Jmt</t>
+          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>402278.058568859</v>
+        <v>402404</v>
       </c>
       <c r="R6" t="n">
-        <v>7011572.709634017</v>
+        <v>7011782</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1250,27 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringbarkad gran.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,49 +1213,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ingela Källén</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ingela Källén</t>
+          <t>Samuel Persson, Sten Svantesson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106607397</v>
+        <v>75954857</v>
       </c>
       <c r="B7" t="n">
-        <v>57193</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>100110</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1336,24 +1259,30 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Språngsdalen, Jmt</t>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>402401.2067675561</v>
+        <v>402220</v>
       </c>
       <c r="R7" t="n">
-        <v>7011730.067199913</v>
+        <v>7011494</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,22 +1306,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:41</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-02-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>21:41</t>
+          <t>2019-02-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,27 +1326,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Katarina Wiklund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Katarina Wiklund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116971869</v>
+        <v>77575598</v>
       </c>
       <c r="B8" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,46 +1349,53 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Språngsdalen, Jmt</t>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>402401</v>
+        <v>402220</v>
       </c>
       <c r="R8" t="n">
-        <v>7011730</v>
+        <v>7011494</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,12 +1419,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2019-05-06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-15</t>
+          <t>2019-05-06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,22 +1439,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Katarina Wiklund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Katarina Wiklund</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126986909</v>
+        <v>77321358</v>
       </c>
       <c r="B9" t="n">
-        <v>88735</v>
+        <v>58209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1541,40 +1462,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>102980</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ottsjö, Jmt</t>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>402449</v>
+        <v>402220</v>
       </c>
       <c r="R9" t="n">
-        <v>7012086</v>
+        <v>7011494</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1598,12 +1528,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-04-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-04-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,70 +1542,78 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126986908</v>
+        <v>77321372</v>
       </c>
       <c r="B10" t="n">
-        <v>91786</v>
+        <v>58497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>102990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ottsjö, Jmt</t>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402449</v>
+        <v>402220</v>
       </c>
       <c r="R10" t="n">
-        <v>7012086</v>
+        <v>7011494</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1699,12 +1637,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-04-26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-04-26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,46 +1651,45 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126986901</v>
+        <v>77081745</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>58327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1769,23 +1706,23 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Högåsen, Ottsjö, Undersåker, Jmt</t>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>402404</v>
+        <v>402220</v>
       </c>
       <c r="R11" t="n">
-        <v>7011782</v>
+        <v>7011494</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1809,22 +1746,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2019-04-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2019-04-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,15 +1766,1924 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Samuel Persson, Sten Svantesson</t>
+          <t>Maud Tyboni</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>116431446</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ottsjö Högåsvägen 64, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>402236</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7011515</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>116971869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Språngsdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>402401</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7011730</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-15</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>77346703</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-04-27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-04-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Kollade in holk.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>73149496</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>402284</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7011510</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>76251833</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-03-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>73149508</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>402284</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7011510</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>76251818</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2019-03-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115795575</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ottsjö Högåsvägen 64, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>402236</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7011515</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En ensam som verkade sjuk, satt på marken och såg tussig och vilsen ut.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115834616</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ottsjö Högåsvägen 64, Ottsjö Högåsvägen 64, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>402237</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7011515</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-04-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>77668511</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2019-05-11</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mycket aggressiv mot bergfinkar, bofinkar, talgoxe m fl.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>73149478</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>402284</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7011510</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2018-09-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>76774761</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-04-03</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-04-03</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>106607397</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56522</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>206004</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skogshare</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lepus timidus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Språngsdalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>402401</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7011730</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-02-10</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>21:41</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Katarina Wiklund</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>73922646</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>402284</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7011510</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2018-11-08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1 mindre klövspår och ett större.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>75813244</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56689</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>206046</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Älg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-01-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-01-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>78532995</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Undersåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>402220</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7011494</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2019-06-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2019-06-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nedre delen av Högåsvägen.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>78559940</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högåsvägen, Ottsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>402284</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7011510</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2019-06-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maud Tyboni</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27634-2025 artfynd.xlsx
+++ b/artfynd/A 27634-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126986909</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126986908</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73260110</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85376911</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126986901</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75954857</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77575598</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77321358</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77321372</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77081745</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116431446</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116971869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77346703</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2224,6 +2294,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73149496</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2333,6 +2408,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76251833</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2442,6 +2522,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73149508</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2551,6 +2636,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76251818</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2662,6 +2752,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115795575</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2783,6 +2878,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115834616</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77668511</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3006,6 +3111,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73149478</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3115,6 +3225,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76774761</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3232,6 +3347,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106607397</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3346,6 +3466,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73922646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3459,6 +3584,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75813244</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3574,6 +3704,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78532995</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3684,8 +3819,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78559940</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>